--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43693C3C-CD97-40FF-9D0F-87EF7CCFF7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392D58EF-ADCF-43FB-9627-2EC530CE470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{1709A316-997D-4FA2-A4D0-9BB9FDF2B51D}"/>
   </bookViews>
@@ -178,24 +178,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -203,22 +188,34 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -543,202 +540,202 @@
   </cols>
   <sheetData>
     <row r="5" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D6" s="9">
+      <c r="D6" s="4">
         <v>45689</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D7" s="9">
+      <c r="D7" s="4">
         <v>45695</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D8" s="9">
+      <c r="D8" s="4">
         <v>45703</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D9" s="9">
+      <c r="D9" s="4">
         <v>45710</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D10" s="9">
+      <c r="D10" s="4">
         <v>45717</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D11" s="9">
+      <c r="D11" s="4">
         <v>45724</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D12" s="9">
+      <c r="D12" s="4">
         <v>45731</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D13" s="9">
+      <c r="D13" s="4">
         <v>45738</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D14" s="9">
+      <c r="D14" s="4">
         <v>45745</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D15" s="9">
+      <c r="D15" s="4">
         <v>45752</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D16" s="9">
+      <c r="D16" s="4">
         <v>45759</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D17" s="9">
+      <c r="D17" s="4">
         <v>45766</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D18" s="9">
+      <c r="D18" s="4">
         <v>45773</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D19" s="9">
+      <c r="D19" s="4">
         <v>45780</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D20" s="9">
+      <c r="D20" s="4">
         <v>45787</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D21" s="9">
+      <c r="D21" s="4">
         <v>45794</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D22" s="1"/>
@@ -749,23 +746,23 @@
       </c>
     </row>
     <row r="24" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="1"/>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="1"/>
@@ -778,25 +775,33 @@
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E10:I10"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="E27:I27"/>
     <mergeCell ref="E28:I28"/>
@@ -808,14 +813,6 @@
     <mergeCell ref="E25:I25"/>
     <mergeCell ref="E20:I21"/>
     <mergeCell ref="E18:I19"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="E13:I13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
